--- a/Excel/Project/Freshmart/Cleaned/Cleaned_FreshMart_Stores.xlsx
+++ b/Excel/Project/Freshmart/Cleaned/Cleaned_FreshMart_Stores.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/AB6FF4EDD41B64DB/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{E1070C48-8906-408E-BF9E-E1DA9BFD639E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD24B5C2-9D66-4C97-BEFB-97637E297BD2}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{234552B8-3EB0-431B-96BB-3BA73C245FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48472A89-63F5-4475-B51F-E373854B1AA0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{E5ADD253-A30B-4D33-902D-D753A01AB6A1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E5ADD253-A30B-4D33-902D-D753A01AB6A1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Stores" sheetId="1" r:id="rId1"/>
     <sheet name="Data_profiling" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -1925,65 +1925,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="13">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF1F4E78"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2138,6 +2079,7 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -2156,6 +2098,64 @@
         <scheme val="none"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1F4E78"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2170,22 +2170,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{642F2EFF-B706-4C76-B172-DE5EBB6FAA35}" name="Table1" displayName="Table1" ref="A1:K181" totalsRowShown="0" headerRowDxfId="1" dataDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{642F2EFF-B706-4C76-B172-DE5EBB6FAA35}" name="Store" displayName="Store" ref="A1:K181" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
   <autoFilter ref="A1:K181" xr:uid="{642F2EFF-B706-4C76-B172-DE5EBB6FAA35}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{18F01F03-64F2-4CD9-80DB-7F1246576F09}" name="Store_ID" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{6DCEEF5D-1C36-47D2-8AB2-08C8F5D04266}" name="Store_Name" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{87D9EA77-F053-4AB6-B0CD-30593E643857}" name="Store_Name2" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{18F01F03-64F2-4CD9-80DB-7F1246576F09}" name="Store_ID" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{6DCEEF5D-1C36-47D2-8AB2-08C8F5D04266}" name="Store_Name" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{87D9EA77-F053-4AB6-B0CD-30593E643857}" name="Store_Name2" dataDxfId="8">
       <calculatedColumnFormula>TRIM(B2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{A5D634DD-9C1D-4CED-91F5-4E8553708F85}" name="Manager" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{C1831E41-9DDD-4D6F-AF99-70590E353703}" name="Region" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{F1ED44E5-81ED-4595-AD84-D50AE09647A5}" name="City" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{3FE16E6C-89CA-4C1E-B5A9-264D64CF6855}" name="State" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{BC631D65-82E5-47D1-87EB-2F1695C001DB}" name="Store_Type" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{B91BE21A-5C58-4314-B77F-967EE27CDA8C}" name="Opening_Date" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{A3ADAE18-A23E-4660-AA80-6385D03EDC85}" name="Monthly_Target" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{2F757317-D0AD-4413-9482-D1BCC6E6B34F}" name="Status" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{A5D634DD-9C1D-4CED-91F5-4E8553708F85}" name="Manager" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{C1831E41-9DDD-4D6F-AF99-70590E353703}" name="Region" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{F1ED44E5-81ED-4595-AD84-D50AE09647A5}" name="City" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{3FE16E6C-89CA-4C1E-B5A9-264D64CF6855}" name="State" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{BC631D65-82E5-47D1-87EB-2F1695C001DB}" name="Store_Type" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{B91BE21A-5C58-4314-B77F-967EE27CDA8C}" name="Opening_Date" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{A3ADAE18-A23E-4660-AA80-6385D03EDC85}" name="Monthly_Target" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{2F757317-D0AD-4413-9482-D1BCC6E6B34F}" name="Status" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2509,21 +2509,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B434AF8D-6537-4BC3-A708-4FD4F3B5FBC1}">
   <dimension ref="A1:K181"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
     <col min="2" max="2" width="32" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="13.54296875" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="17.1796875" customWidth="1"/>
-    <col min="10" max="10" width="18.08984375" customWidth="1"/>
+    <col min="9" max="9" width="17.140625" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>585</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>575</v>
       </c>
@@ -2594,7 +2594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>572</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>569</v>
       </c>
@@ -2666,7 +2666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>566</v>
       </c>
@@ -2702,7 +2702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>563</v>
       </c>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>560</v>
       </c>
@@ -2774,7 +2774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>557</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>554</v>
       </c>
@@ -2846,7 +2846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>551</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>548</v>
       </c>
@@ -2918,7 +2918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>545</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>542</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>539</v>
       </c>
@@ -3026,7 +3026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>537</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>534</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>531</v>
       </c>
@@ -3134,7 +3134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>529</v>
       </c>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>526</v>
       </c>
@@ -3206,7 +3206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>523</v>
       </c>
@@ -3242,7 +3242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>521</v>
       </c>
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>518</v>
       </c>
@@ -3314,7 +3314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>515</v>
       </c>
@@ -3350,7 +3350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>512</v>
       </c>
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>509</v>
       </c>
@@ -3422,7 +3422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>506</v>
       </c>
@@ -3458,7 +3458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>503</v>
       </c>
@@ -3494,7 +3494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>500</v>
       </c>
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>497</v>
       </c>
@@ -3566,7 +3566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>495</v>
       </c>
@@ -3602,7 +3602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>492</v>
       </c>
@@ -3638,7 +3638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>489</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>486</v>
       </c>
@@ -3710,7 +3710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>483</v>
       </c>
@@ -3746,7 +3746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>481</v>
       </c>
@@ -3782,7 +3782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>478</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>475</v>
       </c>
@@ -3854,7 +3854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>472</v>
       </c>
@@ -3890,7 +3890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>469</v>
       </c>
@@ -3926,7 +3926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>466</v>
       </c>
@@ -3962,7 +3962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>463</v>
       </c>
@@ -3998,7 +3998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>460</v>
       </c>
@@ -4034,7 +4034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>457</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>454</v>
       </c>
@@ -4106,7 +4106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>451</v>
       </c>
@@ -4142,7 +4142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>448</v>
       </c>
@@ -4178,7 +4178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>445</v>
       </c>
@@ -4214,7 +4214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>442</v>
       </c>
@@ -4250,7 +4250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>439</v>
       </c>
@@ -4286,7 +4286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>436</v>
       </c>
@@ -4322,7 +4322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>433</v>
       </c>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>430</v>
       </c>
@@ -4394,7 +4394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>427</v>
       </c>
@@ -4430,7 +4430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>424</v>
       </c>
@@ -4466,7 +4466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>421</v>
       </c>
@@ -4502,7 +4502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>418</v>
       </c>
@@ -4538,7 +4538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>415</v>
       </c>
@@ -4574,7 +4574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>412</v>
       </c>
@@ -4610,7 +4610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>409</v>
       </c>
@@ -4646,7 +4646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>406</v>
       </c>
@@ -4682,7 +4682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>403</v>
       </c>
@@ -4718,7 +4718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>400</v>
       </c>
@@ -4754,7 +4754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>397</v>
       </c>
@@ -4790,7 +4790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>394</v>
       </c>
@@ -4826,7 +4826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>391</v>
       </c>
@@ -4862,7 +4862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>388</v>
       </c>
@@ -4896,7 +4896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>386</v>
       </c>
@@ -4932,7 +4932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>383</v>
       </c>
@@ -4966,7 +4966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>381</v>
       </c>
@@ -5002,7 +5002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>377</v>
       </c>
@@ -5038,7 +5038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>374</v>
       </c>
@@ -5074,7 +5074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>371</v>
       </c>
@@ -5110,7 +5110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>368</v>
       </c>
@@ -5146,7 +5146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>365</v>
       </c>
@@ -5182,7 +5182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>362</v>
       </c>
@@ -5218,7 +5218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>359</v>
       </c>
@@ -5254,7 +5254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>356</v>
       </c>
@@ -5290,7 +5290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>351</v>
       </c>
@@ -5326,7 +5326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>347</v>
       </c>
@@ -5362,7 +5362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>344</v>
       </c>
@@ -5398,7 +5398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>341</v>
       </c>
@@ -5434,7 +5434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>337</v>
       </c>
@@ -5470,7 +5470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>333</v>
       </c>
@@ -5506,7 +5506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>330</v>
       </c>
@@ -5542,7 +5542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>327</v>
       </c>
@@ -5576,7 +5576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>325</v>
       </c>
@@ -5612,7 +5612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>322</v>
       </c>
@@ -5648,7 +5648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>318</v>
       </c>
@@ -5684,7 +5684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>315</v>
       </c>
@@ -5720,7 +5720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>312</v>
       </c>
@@ -5756,7 +5756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>308</v>
       </c>
@@ -5792,7 +5792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>303</v>
       </c>
@@ -5828,7 +5828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>299</v>
       </c>
@@ -5864,7 +5864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>294</v>
       </c>
@@ -5900,7 +5900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>291</v>
       </c>
@@ -5936,7 +5936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>288</v>
       </c>
@@ -5972,7 +5972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>285</v>
       </c>
@@ -6008,7 +6008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>282</v>
       </c>
@@ -6044,7 +6044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>279</v>
       </c>
@@ -6080,7 +6080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>276</v>
       </c>
@@ -6116,7 +6116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>273</v>
       </c>
@@ -6152,7 +6152,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>269</v>
       </c>
@@ -6188,7 +6188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>266</v>
       </c>
@@ -6224,7 +6224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>263</v>
       </c>
@@ -6260,7 +6260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>260</v>
       </c>
@@ -6296,7 +6296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>257</v>
       </c>
@@ -6330,7 +6330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>255</v>
       </c>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>252</v>
       </c>
@@ -6402,7 +6402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>250</v>
       </c>
@@ -6438,7 +6438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>247</v>
       </c>
@@ -6474,7 +6474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>244</v>
       </c>
@@ -6510,7 +6510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>241</v>
       </c>
@@ -6546,7 +6546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>238</v>
       </c>
@@ -6582,7 +6582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>235</v>
       </c>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>232</v>
       </c>
@@ -6654,7 +6654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>229</v>
       </c>
@@ -6690,7 +6690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>226</v>
       </c>
@@ -6726,7 +6726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>223</v>
       </c>
@@ -6762,7 +6762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>219</v>
       </c>
@@ -6798,7 +6798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>216</v>
       </c>
@@ -6834,7 +6834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>213</v>
       </c>
@@ -6870,7 +6870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>210</v>
       </c>
@@ -6906,7 +6906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>207</v>
       </c>
@@ -6942,7 +6942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>204</v>
       </c>
@@ -6978,7 +6978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>201</v>
       </c>
@@ -7014,7 +7014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>198</v>
       </c>
@@ -7050,7 +7050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>195</v>
       </c>
@@ -7086,7 +7086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>192</v>
       </c>
@@ -7122,7 +7122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>189</v>
       </c>
@@ -7158,7 +7158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>186</v>
       </c>
@@ -7194,7 +7194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>183</v>
       </c>
@@ -7230,7 +7230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>180</v>
       </c>
@@ -7266,7 +7266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>177</v>
       </c>
@@ -7302,7 +7302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>174</v>
       </c>
@@ -7338,7 +7338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>171</v>
       </c>
@@ -7374,7 +7374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>168</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>164</v>
       </c>
@@ -7446,7 +7446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>161</v>
       </c>
@@ -7482,7 +7482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>157</v>
       </c>
@@ -7518,7 +7518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>153</v>
       </c>
@@ -7554,7 +7554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>148</v>
       </c>
@@ -7590,7 +7590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>142</v>
       </c>
@@ -7626,7 +7626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>139</v>
       </c>
@@ -7662,7 +7662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>136</v>
       </c>
@@ -7698,7 +7698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>133</v>
       </c>
@@ -7734,7 +7734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>130</v>
       </c>
@@ -7770,7 +7770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>127</v>
       </c>
@@ -7806,7 +7806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>124</v>
       </c>
@@ -7842,7 +7842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>121</v>
       </c>
@@ -7878,7 +7878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>117</v>
       </c>
@@ -7914,7 +7914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>114</v>
       </c>
@@ -7950,7 +7950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>111</v>
       </c>
@@ -7986,7 +7986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>108</v>
       </c>
@@ -8022,7 +8022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>105</v>
       </c>
@@ -8058,7 +8058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>102</v>
       </c>
@@ -8094,7 +8094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>99</v>
       </c>
@@ -8130,7 +8130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>96</v>
       </c>
@@ -8166,7 +8166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>91</v>
       </c>
@@ -8202,7 +8202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>88</v>
       </c>
@@ -8238,7 +8238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>85</v>
       </c>
@@ -8274,7 +8274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>82</v>
       </c>
@@ -8310,7 +8310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>79</v>
       </c>
@@ -8318,7 +8318,7 @@
         <v>78</v>
       </c>
       <c r="C162" s="1" t="str">
-        <f t="shared" ref="C162:C193" si="5">TRIM(B162)</f>
+        <f t="shared" ref="C162:C181" si="5">TRIM(B162)</f>
         <v>FreshMart Jaipur Hub</v>
       </c>
       <c r="D162" s="1" t="s">
@@ -8346,7 +8346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>76</v>
       </c>
@@ -8382,7 +8382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>73</v>
       </c>
@@ -8418,7 +8418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>68</v>
       </c>
@@ -8454,7 +8454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>64</v>
       </c>
@@ -8490,7 +8490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>58</v>
       </c>
@@ -8526,7 +8526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>55</v>
       </c>
@@ -8562,7 +8562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>52</v>
       </c>
@@ -8598,7 +8598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>49</v>
       </c>
@@ -8634,7 +8634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>46</v>
       </c>
@@ -8670,7 +8670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>43</v>
       </c>
@@ -8706,7 +8706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>40</v>
       </c>
@@ -8742,7 +8742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>37</v>
       </c>
@@ -8778,7 +8778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>33</v>
       </c>
@@ -8814,7 +8814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>30</v>
       </c>
@@ -8850,7 +8850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>25</v>
       </c>
@@ -8886,7 +8886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>20</v>
       </c>
@@ -8922,7 +8922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>16</v>
       </c>
@@ -8958,7 +8958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>12</v>
       </c>
@@ -8994,7 +8994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>7</v>
       </c>
@@ -9041,15 +9041,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9178D01-33C9-487A-8E3A-8A4FB7E27194}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>586</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>590</v>
       </c>
@@ -9077,7 +9077,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>583</v>
       </c>
@@ -9091,7 +9091,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>576</v>
       </c>
